--- a/data/RPD.xlsx
+++ b/data/RPD.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4506"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\June\Курсы повышения квалификации\ИТМО\repos\ITMO_AI_Top_Teaching\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E44C704-13E9-430B-BD51-D91C274C5165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="11505"/>
   </bookViews>
   <sheets>
     <sheet name="Главный раздел РПД" sheetId="1" r:id="rId1"/>
@@ -19,7 +13,10 @@
     <sheet name="Система оценивания" sheetId="4" r:id="rId4"/>
     <sheet name="Справочник КРМ" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Главный раздел РПД'!$A$5:$M$39</definedName>
+  </definedNames>
+  <calcPr calcId="125725"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="349">
   <si>
     <t>ГЛАВНЫЙ РАЗДЕЛ РАБОЧЕЙ ПРОГРАММЫ ДИСЦИПЛИНЫ</t>
   </si>
@@ -909,84 +906,21 @@
     <t>Б; С</t>
   </si>
   <si>
-    <t>Занятие 1.1. Выборка, эмпирическое распределение и описательная статистика</t>
-  </si>
-  <si>
-    <t>Занятие 1.2. Описательная статистика</t>
-  </si>
-  <si>
-    <t>Занятие 1.3. Статистическая зависимость</t>
-  </si>
-  <si>
     <t xml:space="preserve">Модуль 2. Статистическое оценивание </t>
   </si>
   <si>
-    <t>Занятие 2.1. Точечные оценки и их свойства</t>
-  </si>
-  <si>
-    <t>Занятие 2.2. Методы получения оценок</t>
-  </si>
-  <si>
-    <t>Занятие 2.3. Доверительные интервалы</t>
-  </si>
-  <si>
-    <t>Занятие 2.4. Бутстреп, метод складного ножа, получение оценок в виде доверительных интервалов</t>
-  </si>
-  <si>
     <t>Модуль 3. Статистические гипотезы</t>
   </si>
   <si>
-    <t>Занятие 3.1. Основные определения</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Занятие 3.2. Параметрические и непараметрические критерии </t>
-  </si>
-  <si>
-    <t>Занятие 3.3. Проектирование и анализ A/B-эксперимента</t>
-  </si>
-  <si>
     <t>Модуль 4. Байесовский статистический вывод</t>
   </si>
   <si>
-    <t>Занятие 4.1. Теорема Байеса, априорное и апостериорное распределения</t>
-  </si>
-  <si>
-    <t>Занятие 4.2. MLE, MAP и регуляризация</t>
-  </si>
-  <si>
-    <t>Занятие 4.3. Байесовские доверительные интервалы</t>
-  </si>
-  <si>
-    <t>Занятие 4.4. Байесовский подход в задачах машинного обучения</t>
-  </si>
-  <si>
     <t>Модуль 5. Статистические предсказательные модели</t>
   </si>
   <si>
-    <t>Занятие 5.1. Линейная регрессия как вероятностная модель</t>
-  </si>
-  <si>
-    <t>Занятие 5.2. Задачи регрессии и  модели классификации</t>
-  </si>
-  <si>
-    <t>Занятие 5.3. Регуляризация, качество оценивания моделей и прогноза</t>
-  </si>
-  <si>
     <t>Модуль 6. Валидация и статистическое сравнение моделей машинного обучения</t>
   </si>
   <si>
-    <t>Занятие 6.1. Обобщающая способность и дизайн выборок</t>
-  </si>
-  <si>
-    <t>Занятие 6.2. Кросс-валидация</t>
-  </si>
-  <si>
-    <t>Занятие 6.3. Метрики качества и несбалансированные данные</t>
-  </si>
-  <si>
-    <t>Занятие 6.4. Неопределенность метрик и калибровка</t>
-  </si>
-  <si>
     <t>Проверка гипотез о средних, долях и дисперсиях; парные и независимые выборки; t-, z- и χ²-критерии; критерии согласия, критерий Манна-Уитни.</t>
   </si>
   <si>
@@ -1023,9 +957,6 @@
     <t>Рубеж</t>
   </si>
   <si>
-    <t>Занятие 1.4. Непараметрические оценки</t>
-  </si>
-  <si>
     <t>Логистическая регрессия; логит и пробит модели;  вероятностная интерпретация классификации; модель AR; статистическая причинность.</t>
   </si>
   <si>
@@ -1087,12 +1018,78 @@
   </si>
   <si>
     <t>Модуль 1. Выборка, разведочный и непараметрический анализ данных</t>
+  </si>
+  <si>
+    <t>Тема 1.1. Выборка, эмпирическое распределение и описательная статистика</t>
+  </si>
+  <si>
+    <t>Тема 1.2. Описательная статистика</t>
+  </si>
+  <si>
+    <t>Тема 1.3. Статистическая зависимость</t>
+  </si>
+  <si>
+    <t>Тема 1.4. Непараметрические оценки</t>
+  </si>
+  <si>
+    <t>Тема 2.1. Точечные оценки и их свойства</t>
+  </si>
+  <si>
+    <t>Тема 2.2. Методы получения оценок</t>
+  </si>
+  <si>
+    <t>Тема 2.3. Доверительные интервалы</t>
+  </si>
+  <si>
+    <t>Тема 2.4. Бутстреп, метод складного ножа, получение оценок в виде доверительных интервалов</t>
+  </si>
+  <si>
+    <t>Тема 3.1. Основные определения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тема 3.2. Параметрические и непараметрические критерии </t>
+  </si>
+  <si>
+    <t>Тема 3.3. Проектирование и анализ A/B-эксперимента</t>
+  </si>
+  <si>
+    <t>Тема 4.1. Теорема Байеса, априорное и апостериорное распределения</t>
+  </si>
+  <si>
+    <t>Тема 4.2. MLE, MAP и регуляризация</t>
+  </si>
+  <si>
+    <t>Тема 4.3. Байесовские доверительные интервалы</t>
+  </si>
+  <si>
+    <t>Тема 4.4. Байесовский подход в задачах машинного обучения</t>
+  </si>
+  <si>
+    <t>Тема 5.1. Линейная регрессия как вероятностная модель</t>
+  </si>
+  <si>
+    <t>Тема 5.2. Задачи регрессии и  модели классификации</t>
+  </si>
+  <si>
+    <t>Тема 5.3. Регуляризация, качество оценивания моделей и прогноза</t>
+  </si>
+  <si>
+    <t>Тема 6.1. Обобщающая способность и дизайн выборок</t>
+  </si>
+  <si>
+    <t>Тема 6.2. Кросс-валидация</t>
+  </si>
+  <si>
+    <t>Тема 6.3. Метрики качества и несбалансированные данные</t>
+  </si>
+  <si>
+    <t>Тема 6.4. Неопределенность метрик и калибровка</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="23">
     <font>
       <sz val="11"/>
@@ -1464,7 +1461,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1704,14 +1701,59 @@
     <xf numFmtId="49" fontId="21" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1728,62 +1770,110 @@
     <xf numFmtId="0" fontId="20" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1812,99 +1902,21 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1932,14 +1944,14 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2106,55 +2118,55 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M39"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="31.9140625" customWidth="1"/>
-    <col min="2" max="2" width="54.6640625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="8.1640625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="31.875" customWidth="1"/>
+    <col min="2" max="2" width="54.625" customWidth="1"/>
+    <col min="3" max="3" width="7.5" customWidth="1"/>
+    <col min="4" max="4" width="8.125" customWidth="1"/>
     <col min="5" max="5" width="10.25" customWidth="1"/>
-    <col min="6" max="6" width="10.58203125" customWidth="1"/>
-    <col min="7" max="7" width="38.08203125" customWidth="1"/>
-    <col min="8" max="8" width="8.4140625" customWidth="1"/>
-    <col min="9" max="9" width="10.4140625" customWidth="1"/>
-    <col min="10" max="10" width="8.4140625" customWidth="1"/>
+    <col min="6" max="6" width="10.625" customWidth="1"/>
+    <col min="7" max="7" width="38.125" customWidth="1"/>
+    <col min="8" max="8" width="8.375" customWidth="1"/>
+    <col min="9" max="9" width="10.375" customWidth="1"/>
+    <col min="10" max="10" width="8.375" customWidth="1"/>
     <col min="11" max="11" width="5.25" customWidth="1"/>
     <col min="12" max="12" width="26" customWidth="1"/>
     <col min="13" max="13" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="17" hidden="1" customHeight="1">
-      <c r="A1" s="98" t="s">
+    <row r="1" spans="1:13" ht="17.100000000000001" hidden="1" customHeight="1">
+      <c r="A1" s="89" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
       <c r="I1" s="45"/>
       <c r="J1" s="45"/>
       <c r="K1" s="16"/>
-      <c r="L1" s="98" t="s">
+      <c r="L1" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="98"/>
+      <c r="M1" s="89"/>
     </row>
     <row r="2" spans="1:13" ht="15" hidden="1" customHeight="1">
-      <c r="A2" s="99" t="s">
+      <c r="A2" s="90" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
       <c r="I2" s="46"/>
       <c r="J2" s="46"/>
       <c r="K2" s="16"/>
@@ -2166,17 +2178,17 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="29" hidden="1" customHeight="1">
-      <c r="A3" s="100" t="s">
+    <row r="3" spans="1:13" ht="29.1" hidden="1" customHeight="1">
+      <c r="A3" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="100"/>
-      <c r="C3" s="100"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="100"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="100"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="91"/>
       <c r="I3" s="47"/>
       <c r="J3" s="47"/>
       <c r="K3" s="16"/>
@@ -2189,16 +2201,16 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" hidden="1" customHeight="1">
-      <c r="A4" s="101" t="s">
+      <c r="A4" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="101"/>
-      <c r="C4" s="101"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="101"/>
-      <c r="H4" s="101"/>
+      <c r="B4" s="92"/>
+      <c r="C4" s="92"/>
+      <c r="D4" s="92"/>
+      <c r="E4" s="92"/>
+      <c r="F4" s="92"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="92"/>
       <c r="I4" s="48"/>
       <c r="J4" s="48"/>
       <c r="K4" s="16"/>
@@ -2210,7 +2222,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="34" customHeight="1">
+    <row r="5" spans="1:13" ht="33.950000000000003" customHeight="1">
       <c r="A5" s="21" t="s">
         <v>8</v>
       </c>
@@ -2230,16 +2242,16 @@
         <v>13</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>341</v>
+        <v>319</v>
       </c>
       <c r="H5" s="23" t="s">
         <v>14</v>
       </c>
       <c r="I5" s="49" t="s">
-        <v>317</v>
+        <v>296</v>
       </c>
       <c r="J5" s="49" t="s">
-        <v>318</v>
+        <v>297</v>
       </c>
       <c r="K5" s="16"/>
       <c r="L5" s="19" t="s">
@@ -2251,7 +2263,7 @@
     </row>
     <row r="6" spans="1:13" ht="30.4" customHeight="1">
       <c r="A6" s="55" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="B6" s="24" t="s">
         <v>16</v>
@@ -2267,17 +2279,17 @@
         <v>17</v>
       </c>
       <c r="F6" s="71" t="s">
-        <v>346</v>
+        <v>324</v>
       </c>
       <c r="G6" s="71"/>
       <c r="H6" s="72" t="s">
         <v>288</v>
       </c>
       <c r="I6" s="73" t="s">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="J6" s="73" t="s">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="K6" s="16"/>
       <c r="L6" s="16"/>
@@ -2288,7 +2300,7 @@
     </row>
     <row r="7" spans="1:13" ht="57" customHeight="1">
       <c r="A7" s="54" t="s">
-        <v>289</v>
+        <v>327</v>
       </c>
       <c r="B7" s="56" t="s">
         <v>268</v>
@@ -2299,23 +2311,23 @@
       <c r="D7" s="59">
         <v>2</v>
       </c>
-      <c r="E7" s="81" t="s">
+      <c r="E7" s="93" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="81" t="s">
+      <c r="F7" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="84" t="s">
+      <c r="G7" s="99" t="s">
         <v>229</v>
       </c>
       <c r="H7" s="61" t="s">
         <v>21</v>
       </c>
       <c r="I7" s="61" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="J7" s="61" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="K7" s="16"/>
       <c r="L7" s="16"/>
@@ -2323,7 +2335,7 @@
     </row>
     <row r="8" spans="1:13" ht="40.5" customHeight="1">
       <c r="A8" s="54" t="s">
-        <v>290</v>
+        <v>328</v>
       </c>
       <c r="B8" s="57" t="s">
         <v>269</v>
@@ -2334,73 +2346,69 @@
       <c r="D8" s="61">
         <v>2</v>
       </c>
-      <c r="E8" s="82"/>
-      <c r="F8" s="82"/>
-      <c r="G8" s="85"/>
+      <c r="E8" s="95"/>
+      <c r="F8" s="95"/>
+      <c r="G8" s="100"/>
       <c r="H8" s="61" t="s">
         <v>21</v>
       </c>
       <c r="I8" s="61" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="J8" s="61" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="K8" s="16"/>
       <c r="L8" s="16"/>
       <c r="M8" s="16"/>
     </row>
-    <row r="9" spans="1:13" ht="17" customHeight="1">
-      <c r="A9" s="104" t="s">
-        <v>291</v>
-      </c>
-      <c r="B9" s="106" t="s">
+    <row r="9" spans="1:13" ht="17.100000000000001" customHeight="1">
+      <c r="A9" s="85" t="s">
         <v>329</v>
       </c>
-      <c r="C9" s="59" t="s">
+      <c r="B9" s="87" t="s">
+        <v>307</v>
+      </c>
+      <c r="C9" s="162" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="59">
-        <v>2</v>
-      </c>
-      <c r="E9" s="82"/>
-      <c r="F9" s="82"/>
-      <c r="G9" s="85"/>
-      <c r="H9" s="81" t="s">
+      <c r="D9" s="104">
+        <v>4</v>
+      </c>
+      <c r="E9" s="95"/>
+      <c r="F9" s="95"/>
+      <c r="G9" s="100"/>
+      <c r="H9" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="I9" s="81" t="s">
-        <v>330</v>
-      </c>
-      <c r="J9" s="81" t="s">
-        <v>332</v>
+      <c r="I9" s="93" t="s">
+        <v>308</v>
+      </c>
+      <c r="J9" s="93" t="s">
+        <v>310</v>
       </c>
       <c r="K9" s="16"/>
       <c r="L9" s="16"/>
       <c r="M9" s="16"/>
     </row>
     <row r="10" spans="1:13" ht="39" customHeight="1">
-      <c r="A10" s="105"/>
-      <c r="B10" s="107"/>
-      <c r="C10" s="59" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="59">
-        <v>2</v>
-      </c>
-      <c r="E10" s="83"/>
-      <c r="F10" s="83"/>
-      <c r="G10" s="86"/>
-      <c r="H10" s="83"/>
-      <c r="I10" s="83"/>
-      <c r="J10" s="83"/>
+      <c r="A10" s="86"/>
+      <c r="B10" s="88"/>
+      <c r="C10" s="163"/>
+      <c r="D10" s="164"/>
+      <c r="E10" s="94"/>
+      <c r="F10" s="94"/>
+      <c r="G10" s="101"/>
+      <c r="H10" s="94"/>
+      <c r="I10" s="94"/>
+      <c r="J10" s="94"/>
       <c r="K10" s="16"/>
       <c r="L10" s="16"/>
       <c r="M10" s="16"/>
     </row>
     <row r="11" spans="1:13" ht="58.5" customHeight="1">
       <c r="A11" s="54" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B11" s="57" t="s">
         <v>270</v>
@@ -2418,16 +2426,16 @@
         <v>27</v>
       </c>
       <c r="G11" s="75" t="s">
-        <v>347</v>
+        <v>325</v>
       </c>
       <c r="H11" s="61" t="s">
         <v>19</v>
       </c>
       <c r="I11" s="61" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="J11" s="61" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="K11" s="16"/>
       <c r="L11" s="16"/>
@@ -2435,7 +2443,7 @@
     </row>
     <row r="12" spans="1:13" ht="32.25" customHeight="1">
       <c r="A12" s="55" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B12" s="58" t="s">
         <v>16</v>
@@ -2458,18 +2466,18 @@
         <v>288</v>
       </c>
       <c r="I12" s="50" t="s">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="J12" s="50" t="s">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="K12" s="16"/>
       <c r="L12" s="16"/>
       <c r="M12" s="16"/>
     </row>
-    <row r="13" spans="1:13" ht="32" customHeight="1">
+    <row r="13" spans="1:13" ht="32.1" customHeight="1">
       <c r="A13" s="54" t="s">
-        <v>293</v>
+        <v>331</v>
       </c>
       <c r="B13" s="57" t="s">
         <v>271</v>
@@ -2480,31 +2488,31 @@
       <c r="D13" s="61">
         <v>2</v>
       </c>
-      <c r="E13" s="81" t="s">
+      <c r="E13" s="93" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="81" t="s">
+      <c r="F13" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="G13" s="89" t="s">
+      <c r="G13" s="96" t="s">
         <v>229</v>
       </c>
       <c r="H13" s="61" t="s">
         <v>21</v>
       </c>
       <c r="I13" s="70" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="J13" s="63" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="K13" s="16"/>
       <c r="L13" s="16"/>
       <c r="M13" s="16"/>
     </row>
-    <row r="14" spans="1:13" ht="34" customHeight="1">
+    <row r="14" spans="1:13" ht="33.950000000000003" customHeight="1">
       <c r="A14" s="54" t="s">
-        <v>294</v>
+        <v>332</v>
       </c>
       <c r="B14" s="56" t="s">
         <v>272</v>
@@ -2515,25 +2523,25 @@
       <c r="D14" s="59">
         <v>2</v>
       </c>
-      <c r="E14" s="82"/>
-      <c r="F14" s="82"/>
-      <c r="G14" s="90"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="97"/>
       <c r="H14" s="59" t="s">
         <v>19</v>
       </c>
       <c r="I14" s="59" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="J14" s="60" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="K14" s="16"/>
       <c r="L14" s="16"/>
       <c r="M14" s="16"/>
     </row>
-    <row r="15" spans="1:13" ht="34" customHeight="1">
+    <row r="15" spans="1:13" ht="33.950000000000003" customHeight="1">
       <c r="A15" s="54" t="s">
-        <v>295</v>
+        <v>333</v>
       </c>
       <c r="B15" s="57" t="s">
         <v>273</v>
@@ -2544,25 +2552,25 @@
       <c r="D15" s="61">
         <v>2</v>
       </c>
-      <c r="E15" s="82"/>
-      <c r="F15" s="82"/>
-      <c r="G15" s="90"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="97"/>
       <c r="H15" s="61" t="s">
         <v>19</v>
       </c>
       <c r="I15" s="76" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="J15" s="77" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="K15" s="16"/>
       <c r="L15" s="16"/>
       <c r="M15" s="16"/>
     </row>
-    <row r="16" spans="1:13" ht="68.5" customHeight="1">
+    <row r="16" spans="1:13" ht="68.45" customHeight="1">
       <c r="A16" s="54" t="s">
-        <v>296</v>
+        <v>334</v>
       </c>
       <c r="B16" s="56" t="s">
         <v>274</v>
@@ -2573,25 +2581,25 @@
       <c r="D16" s="59">
         <v>2</v>
       </c>
-      <c r="E16" s="83"/>
-      <c r="F16" s="83"/>
-      <c r="G16" s="91"/>
+      <c r="E16" s="94"/>
+      <c r="F16" s="94"/>
+      <c r="G16" s="98"/>
       <c r="H16" s="59" t="s">
         <v>19</v>
       </c>
       <c r="I16" s="59" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="J16" s="60" t="s">
-        <v>331</v>
+        <v>309</v>
       </c>
       <c r="K16" s="16"/>
       <c r="L16" s="16"/>
       <c r="M16" s="16"/>
     </row>
-    <row r="17" spans="1:13" ht="33.9" customHeight="1">
+    <row r="17" spans="1:13" ht="33.950000000000003" customHeight="1">
       <c r="A17" s="55" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B17" s="58" t="s">
         <v>16</v>
@@ -2614,18 +2622,18 @@
         <v>288</v>
       </c>
       <c r="I17" s="50" t="s">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="J17" s="50" t="s">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="K17" s="16"/>
       <c r="L17" s="16"/>
       <c r="M17" s="16"/>
     </row>
-    <row r="18" spans="1:13" ht="34" customHeight="1">
+    <row r="18" spans="1:13" ht="33.950000000000003" customHeight="1">
       <c r="A18" s="54" t="s">
-        <v>298</v>
+        <v>335</v>
       </c>
       <c r="B18" s="57" t="s">
         <v>275</v>
@@ -2636,34 +2644,34 @@
       <c r="D18" s="61">
         <v>4</v>
       </c>
-      <c r="E18" s="81" t="s">
+      <c r="E18" s="93" t="s">
         <v>17</v>
       </c>
-      <c r="F18" s="81" t="s">
+      <c r="F18" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="G18" s="89" t="s">
+      <c r="G18" s="96" t="s">
         <v>234</v>
       </c>
       <c r="H18" s="61" t="s">
         <v>21</v>
       </c>
       <c r="I18" s="76" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="J18" s="77" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="K18" s="16"/>
       <c r="L18" s="16"/>
       <c r="M18" s="16"/>
     </row>
-    <row r="19" spans="1:13" ht="34" customHeight="1">
+    <row r="19" spans="1:13" ht="33.950000000000003" customHeight="1">
       <c r="A19" s="54" t="s">
-        <v>299</v>
+        <v>336</v>
       </c>
       <c r="B19" s="56" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C19" s="59" t="s">
         <v>22</v>
@@ -2671,25 +2679,25 @@
       <c r="D19" s="59">
         <v>6</v>
       </c>
-      <c r="E19" s="83"/>
-      <c r="F19" s="83"/>
-      <c r="G19" s="91"/>
+      <c r="E19" s="94"/>
+      <c r="F19" s="94"/>
+      <c r="G19" s="98"/>
       <c r="H19" s="59" t="s">
         <v>19</v>
       </c>
       <c r="I19" s="59" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="J19" s="60" t="s">
-        <v>331</v>
+        <v>309</v>
       </c>
       <c r="K19" s="16"/>
       <c r="L19" s="16"/>
       <c r="M19" s="16"/>
     </row>
-    <row r="20" spans="1:13" ht="114.5" customHeight="1">
+    <row r="20" spans="1:13" ht="114.6" customHeight="1">
       <c r="A20" s="54" t="s">
-        <v>300</v>
+        <v>337</v>
       </c>
       <c r="B20" s="57" t="s">
         <v>276</v>
@@ -2707,16 +2715,16 @@
         <v>28</v>
       </c>
       <c r="G20" s="74" t="s">
-        <v>342</v>
+        <v>320</v>
       </c>
       <c r="H20" s="61" t="s">
         <v>19</v>
       </c>
       <c r="I20" s="76" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="J20" s="77" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="K20" s="16"/>
       <c r="L20" s="16"/>
@@ -2724,7 +2732,7 @@
     </row>
     <row r="21" spans="1:13" ht="30" customHeight="1">
       <c r="A21" s="55" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="B21" s="58" t="s">
         <v>16</v>
@@ -2747,18 +2755,18 @@
         <v>283</v>
       </c>
       <c r="I21" s="50" t="s">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="J21" s="50" t="s">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="K21" s="16"/>
       <c r="L21" s="16"/>
       <c r="M21" s="16"/>
     </row>
-    <row r="22" spans="1:13" ht="47" customHeight="1">
+    <row r="22" spans="1:13" ht="47.1" customHeight="1">
       <c r="A22" s="54" t="s">
-        <v>302</v>
+        <v>338</v>
       </c>
       <c r="B22" s="57" t="s">
         <v>277</v>
@@ -2769,31 +2777,31 @@
       <c r="D22" s="61">
         <v>2</v>
       </c>
-      <c r="E22" s="81" t="s">
+      <c r="E22" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="F22" s="81" t="s">
+      <c r="F22" s="93" t="s">
         <v>32</v>
       </c>
-      <c r="G22" s="89" t="s">
+      <c r="G22" s="96" t="s">
         <v>239</v>
       </c>
       <c r="H22" s="61" t="s">
         <v>21</v>
       </c>
       <c r="I22" s="76" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="J22" s="77" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="K22" s="16"/>
       <c r="L22" s="16"/>
       <c r="M22" s="16"/>
     </row>
-    <row r="23" spans="1:13" ht="35" customHeight="1">
+    <row r="23" spans="1:13" ht="35.1" customHeight="1">
       <c r="A23" s="54" t="s">
-        <v>303</v>
+        <v>339</v>
       </c>
       <c r="B23" s="56" t="s">
         <v>278</v>
@@ -2804,17 +2812,17 @@
       <c r="D23" s="59">
         <v>2</v>
       </c>
-      <c r="E23" s="83"/>
-      <c r="F23" s="83"/>
-      <c r="G23" s="91"/>
+      <c r="E23" s="94"/>
+      <c r="F23" s="94"/>
+      <c r="G23" s="98"/>
       <c r="H23" s="59" t="s">
         <v>19</v>
       </c>
       <c r="I23" s="59" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="J23" s="60" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="K23" s="16"/>
       <c r="L23" s="16"/>
@@ -2822,7 +2830,7 @@
     </row>
     <row r="24" spans="1:13" ht="55.5" customHeight="1">
       <c r="A24" s="54" t="s">
-        <v>304</v>
+        <v>340</v>
       </c>
       <c r="B24" s="57" t="s">
         <v>279</v>
@@ -2831,25 +2839,25 @@
         <v>20</v>
       </c>
       <c r="D24" s="61">
-        <v>4</v>
-      </c>
-      <c r="E24" s="81" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="F24" s="81" t="s">
+      <c r="F24" s="93" t="s">
         <v>33</v>
       </c>
-      <c r="G24" s="89" t="s">
+      <c r="G24" s="96" t="s">
         <v>243</v>
       </c>
       <c r="H24" s="61" t="s">
         <v>21</v>
       </c>
       <c r="I24" s="76" t="s">
-        <v>330</v>
-      </c>
-      <c r="J24" s="77" t="s">
-        <v>331</v>
+        <v>308</v>
+      </c>
+      <c r="J24" s="82" t="s">
+        <v>310</v>
       </c>
       <c r="K24" s="16"/>
       <c r="L24" s="16"/>
@@ -2857,7 +2865,7 @@
     </row>
     <row r="25" spans="1:13" ht="33" customHeight="1">
       <c r="A25" s="54" t="s">
-        <v>305</v>
+        <v>341</v>
       </c>
       <c r="B25" s="56" t="s">
         <v>280</v>
@@ -2866,19 +2874,19 @@
         <v>22</v>
       </c>
       <c r="D25" s="59">
-        <v>2</v>
-      </c>
-      <c r="E25" s="83"/>
-      <c r="F25" s="83"/>
-      <c r="G25" s="91"/>
+        <v>4</v>
+      </c>
+      <c r="E25" s="94"/>
+      <c r="F25" s="94"/>
+      <c r="G25" s="98"/>
       <c r="H25" s="59" t="s">
         <v>21</v>
       </c>
       <c r="I25" s="59" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="J25" s="59" t="s">
-        <v>332</v>
+        <v>309</v>
       </c>
       <c r="K25" s="16"/>
       <c r="L25" s="16"/>
@@ -2886,7 +2894,7 @@
     </row>
     <row r="26" spans="1:13" ht="32.65" customHeight="1">
       <c r="A26" s="55" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="B26" s="58" t="s">
         <v>16</v>
@@ -2909,18 +2917,18 @@
         <v>283</v>
       </c>
       <c r="I26" s="50" t="s">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="J26" s="50" t="s">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="K26" s="16"/>
       <c r="L26" s="16"/>
       <c r="M26" s="16"/>
     </row>
-    <row r="27" spans="1:13" ht="68.5" customHeight="1">
+    <row r="27" spans="1:13" ht="68.45" customHeight="1">
       <c r="A27" s="54" t="s">
-        <v>307</v>
+        <v>342</v>
       </c>
       <c r="B27" s="56" t="s">
         <v>281</v>
@@ -2944,21 +2952,21 @@
         <v>21</v>
       </c>
       <c r="I27" s="59" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="J27" s="77" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="K27" s="16"/>
       <c r="L27" s="16"/>
       <c r="M27" s="16"/>
     </row>
-    <row r="28" spans="1:13" ht="113.5" customHeight="1">
+    <row r="28" spans="1:13" ht="113.45" customHeight="1">
       <c r="A28" s="54" t="s">
-        <v>308</v>
+        <v>343</v>
       </c>
       <c r="B28" s="56" t="s">
-        <v>328</v>
+        <v>306</v>
       </c>
       <c r="C28" s="59" t="s">
         <v>22</v>
@@ -2979,10 +2987,10 @@
         <v>21</v>
       </c>
       <c r="I28" s="59" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="J28" s="77" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="K28" s="16"/>
       <c r="L28" s="16"/>
@@ -2990,7 +2998,7 @@
     </row>
     <row r="29" spans="1:13" ht="115.5" customHeight="1">
       <c r="A29" s="54" t="s">
-        <v>309</v>
+        <v>344</v>
       </c>
       <c r="B29" s="57" t="s">
         <v>287</v>
@@ -3014,10 +3022,10 @@
         <v>19</v>
       </c>
       <c r="I29" s="76" t="s">
-        <v>330</v>
-      </c>
-      <c r="J29" s="76" t="s">
-        <v>332</v>
+        <v>308</v>
+      </c>
+      <c r="J29" s="81" t="s">
+        <v>309</v>
       </c>
       <c r="K29" s="16"/>
       <c r="L29" s="16"/>
@@ -3025,7 +3033,7 @@
     </row>
     <row r="30" spans="1:13" ht="29.25" customHeight="1">
       <c r="A30" s="55" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="B30" s="58" t="s">
         <v>16</v>
@@ -3048,7 +3056,7 @@
         <v>283</v>
       </c>
       <c r="I30" s="50" t="s">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="J30" s="50"/>
       <c r="K30" s="16"/>
@@ -3057,7 +3065,7 @@
     </row>
     <row r="31" spans="1:13" ht="63" customHeight="1">
       <c r="A31" s="54" t="s">
-        <v>311</v>
+        <v>345</v>
       </c>
       <c r="B31" s="56" t="s">
         <v>284</v>
@@ -3068,31 +3076,31 @@
       <c r="D31" s="59">
         <v>4</v>
       </c>
-      <c r="E31" s="92" t="s">
+      <c r="E31" s="104" t="s">
         <v>24</v>
       </c>
-      <c r="F31" s="92" t="s">
+      <c r="F31" s="104" t="s">
         <v>28</v>
       </c>
-      <c r="G31" s="95" t="s">
+      <c r="G31" s="107" t="s">
         <v>257</v>
       </c>
       <c r="H31" s="59" t="s">
         <v>21</v>
       </c>
       <c r="I31" s="59" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="J31" s="60" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="K31" s="16"/>
       <c r="L31" s="16"/>
       <c r="M31" s="16"/>
     </row>
-    <row r="32" spans="1:13" ht="44.5" customHeight="1">
+    <row r="32" spans="1:13" ht="44.45" customHeight="1">
       <c r="A32" s="54" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="B32" s="57" t="s">
         <v>285</v>
@@ -3103,27 +3111,27 @@
       <c r="D32" s="61">
         <v>4</v>
       </c>
-      <c r="E32" s="93"/>
-      <c r="F32" s="93"/>
-      <c r="G32" s="96"/>
+      <c r="E32" s="105"/>
+      <c r="F32" s="105"/>
+      <c r="G32" s="108"/>
       <c r="H32" s="61" t="s">
         <v>19</v>
       </c>
       <c r="I32" s="61" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="J32" s="62" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="K32" s="16"/>
       <c r="L32" s="16"/>
       <c r="M32" s="16"/>
     </row>
-    <row r="33" spans="1:13" ht="29.5" customHeight="1">
-      <c r="A33" s="102" t="s">
-        <v>313</v>
-      </c>
-      <c r="B33" s="87" t="s">
+    <row r="33" spans="1:13" ht="29.45" customHeight="1">
+      <c r="A33" s="83" t="s">
+        <v>347</v>
+      </c>
+      <c r="B33" s="102" t="s">
         <v>286</v>
       </c>
       <c r="C33" s="59" t="s">
@@ -3132,42 +3140,42 @@
       <c r="D33" s="59">
         <v>4</v>
       </c>
-      <c r="E33" s="93"/>
-      <c r="F33" s="93"/>
-      <c r="G33" s="96"/>
+      <c r="E33" s="105"/>
+      <c r="F33" s="105"/>
+      <c r="G33" s="108"/>
       <c r="H33" s="59" t="s">
         <v>21</v>
       </c>
       <c r="I33" s="59" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="J33" s="60" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="K33" s="16"/>
       <c r="L33" s="16"/>
       <c r="M33" s="16"/>
     </row>
-    <row r="34" spans="1:13" ht="29.5" customHeight="1">
-      <c r="A34" s="103"/>
-      <c r="B34" s="88"/>
+    <row r="34" spans="1:13" ht="29.45" customHeight="1">
+      <c r="A34" s="84"/>
+      <c r="B34" s="103"/>
       <c r="C34" s="59" t="s">
         <v>22</v>
       </c>
       <c r="D34" s="59">
         <v>2</v>
       </c>
-      <c r="E34" s="93"/>
-      <c r="F34" s="93"/>
-      <c r="G34" s="96"/>
+      <c r="E34" s="105"/>
+      <c r="F34" s="105"/>
+      <c r="G34" s="108"/>
       <c r="H34" s="61" t="s">
         <v>21</v>
       </c>
       <c r="I34" s="61" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="J34" s="61" t="s">
-        <v>331</v>
+        <v>310</v>
       </c>
       <c r="K34" s="16"/>
       <c r="L34" s="16"/>
@@ -3175,7 +3183,7 @@
     </row>
     <row r="35" spans="1:13" ht="43.15" customHeight="1">
       <c r="A35" s="54" t="s">
-        <v>314</v>
+        <v>348</v>
       </c>
       <c r="B35" s="57" t="s">
         <v>35</v>
@@ -3186,17 +3194,17 @@
       <c r="D35" s="61">
         <v>2</v>
       </c>
-      <c r="E35" s="94"/>
-      <c r="F35" s="94"/>
-      <c r="G35" s="97"/>
+      <c r="E35" s="106"/>
+      <c r="F35" s="106"/>
+      <c r="G35" s="109"/>
       <c r="H35" s="59" t="s">
         <v>19</v>
       </c>
       <c r="I35" s="59" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="J35" s="60" t="s">
-        <v>331</v>
+        <v>309</v>
       </c>
       <c r="K35" s="16"/>
       <c r="L35" s="16"/>
@@ -3224,16 +3232,16 @@
       <c r="G36" s="29"/>
       <c r="H36" s="30"/>
       <c r="I36" s="30" t="s">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="J36" s="51" t="s">
-        <v>344</v>
+        <v>322</v>
       </c>
       <c r="K36" s="16"/>
       <c r="L36" s="16"/>
       <c r="M36" s="16"/>
     </row>
-    <row r="37" spans="1:13" ht="14.5">
+    <row r="37" spans="1:13">
       <c r="A37" s="31" t="s">
         <v>41</v>
       </c>
@@ -3255,7 +3263,7 @@
       <c r="L37" s="16"/>
       <c r="M37" s="16"/>
     </row>
-    <row r="38" spans="1:13" ht="14.5">
+    <row r="38" spans="1:13">
       <c r="A38" s="35" t="s">
         <v>43</v>
       </c>
@@ -3277,7 +3285,7 @@
       <c r="L38" s="16"/>
       <c r="M38" s="16"/>
     </row>
-    <row r="39" spans="1:13" ht="14.5">
+    <row r="39" spans="1:13">
       <c r="A39" s="35" t="s">
         <v>44</v>
       </c>
@@ -3300,7 +3308,24 @@
       <c r="M39" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <autoFilter ref="A5:M39"/>
+  <mergeCells count="32">
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E7:E10"/>
+    <mergeCell ref="F7:F10"/>
+    <mergeCell ref="G7:G10"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="E31:E35"/>
+    <mergeCell ref="F31:F35"/>
+    <mergeCell ref="G31:G35"/>
+    <mergeCell ref="C9:C10"/>
     <mergeCell ref="A33:A34"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
@@ -3317,29 +3342,16 @@
     <mergeCell ref="F18:F19"/>
     <mergeCell ref="G18:G19"/>
     <mergeCell ref="H9:H10"/>
-    <mergeCell ref="E7:E10"/>
-    <mergeCell ref="F7:F10"/>
-    <mergeCell ref="G7:G10"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="E31:E35"/>
-    <mergeCell ref="F31:F35"/>
-    <mergeCell ref="G31:G35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H47"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
@@ -3348,229 +3360,229 @@
     <col min="6" max="8" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17" customHeight="1">
-      <c r="A1" s="139" t="s">
+    <row r="1" spans="1:8" ht="17.100000000000001" customHeight="1">
+      <c r="A1" s="110" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-    </row>
-    <row r="2" spans="1:8" ht="16" customHeight="1">
-      <c r="A2" s="140" t="s">
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.95" customHeight="1">
+      <c r="A2" s="111" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="140"/>
-      <c r="C2" s="140"/>
-      <c r="D2" s="140"/>
-      <c r="E2" s="140"/>
-      <c r="F2" s="140"/>
-      <c r="G2" s="140"/>
-      <c r="H2" s="140"/>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="141" t="s">
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="111"/>
+      <c r="G2" s="111"/>
+      <c r="H2" s="111"/>
+    </row>
+    <row r="4" spans="1:8" ht="15">
+      <c r="A4" s="112" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="123"/>
-      <c r="C4" s="141" t="s">
+      <c r="B4" s="113"/>
+      <c r="C4" s="112" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="123"/>
-      <c r="E4" s="141" t="s">
+      <c r="D4" s="113"/>
+      <c r="E4" s="112" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="123"/>
-      <c r="G4" s="141" t="s">
+      <c r="F4" s="113"/>
+      <c r="G4" s="112" t="s">
         <v>50</v>
       </c>
-      <c r="H4" s="123"/>
+      <c r="H4" s="113"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="142" t="s">
+      <c r="A5" s="114" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="143"/>
-      <c r="C5" s="142" t="s">
+      <c r="B5" s="115"/>
+      <c r="C5" s="114" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="143"/>
-      <c r="E5" s="142" t="s">
+      <c r="D5" s="115"/>
+      <c r="E5" s="114" t="s">
         <v>53</v>
       </c>
-      <c r="F5" s="143"/>
-      <c r="G5" s="142" t="s">
+      <c r="F5" s="115"/>
+      <c r="G5" s="114" t="s">
         <v>54</v>
       </c>
-      <c r="H5" s="143"/>
+      <c r="H5" s="115"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="144"/>
-      <c r="B6" s="145"/>
-      <c r="C6" s="144"/>
-      <c r="D6" s="145"/>
-      <c r="E6" s="144"/>
-      <c r="F6" s="145"/>
-      <c r="G6" s="144"/>
-      <c r="H6" s="145"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.5">
-      <c r="A8" s="117" t="s">
+      <c r="A6" s="116"/>
+      <c r="B6" s="117"/>
+      <c r="C6" s="116"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="116"/>
+      <c r="F6" s="117"/>
+      <c r="G6" s="116"/>
+      <c r="H6" s="117"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75">
+      <c r="A8" s="118" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="117"/>
-      <c r="C8" s="117"/>
-      <c r="D8" s="117"/>
-      <c r="E8" s="117"/>
-      <c r="F8" s="117"/>
-      <c r="G8" s="117"/>
-      <c r="H8" s="117"/>
+      <c r="B8" s="118"/>
+      <c r="C8" s="118"/>
+      <c r="D8" s="118"/>
+      <c r="E8" s="118"/>
+      <c r="F8" s="118"/>
+      <c r="G8" s="118"/>
+      <c r="H8" s="118"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="130" t="s">
+      <c r="A9" s="119" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="131"/>
-      <c r="C9" s="131"/>
-      <c r="D9" s="131"/>
-      <c r="E9" s="131"/>
-      <c r="F9" s="131"/>
-      <c r="G9" s="131"/>
-      <c r="H9" s="132"/>
+      <c r="B9" s="120"/>
+      <c r="C9" s="120"/>
+      <c r="D9" s="120"/>
+      <c r="E9" s="120"/>
+      <c r="F9" s="120"/>
+      <c r="G9" s="120"/>
+      <c r="H9" s="121"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="133"/>
-      <c r="B10" s="134"/>
-      <c r="C10" s="134"/>
-      <c r="D10" s="134"/>
-      <c r="E10" s="134"/>
-      <c r="F10" s="134"/>
-      <c r="G10" s="134"/>
-      <c r="H10" s="135"/>
+      <c r="A10" s="122"/>
+      <c r="B10" s="123"/>
+      <c r="C10" s="123"/>
+      <c r="D10" s="123"/>
+      <c r="E10" s="123"/>
+      <c r="F10" s="123"/>
+      <c r="G10" s="123"/>
+      <c r="H10" s="124"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="136"/>
-      <c r="B11" s="137"/>
-      <c r="C11" s="137"/>
-      <c r="D11" s="137"/>
-      <c r="E11" s="137"/>
-      <c r="F11" s="137"/>
-      <c r="G11" s="137"/>
-      <c r="H11" s="138"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.5">
-      <c r="A13" s="117" t="s">
+      <c r="A11" s="125"/>
+      <c r="B11" s="126"/>
+      <c r="C11" s="126"/>
+      <c r="D11" s="126"/>
+      <c r="E11" s="126"/>
+      <c r="F11" s="126"/>
+      <c r="G11" s="126"/>
+      <c r="H11" s="127"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75">
+      <c r="A13" s="118" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="117"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="117"/>
-      <c r="E13" s="117"/>
-      <c r="F13" s="117"/>
-      <c r="G13" s="117"/>
-      <c r="H13" s="117"/>
-    </row>
-    <row r="14" spans="1:8" ht="17" customHeight="1">
+      <c r="B13" s="118"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="118"/>
+      <c r="F13" s="118"/>
+      <c r="G13" s="118"/>
+      <c r="H13" s="118"/>
+    </row>
+    <row r="14" spans="1:8" ht="17.100000000000001" customHeight="1">
       <c r="A14" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="124" t="s">
+      <c r="B14" s="128" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="125"/>
-      <c r="D14" s="125"/>
-      <c r="E14" s="125"/>
-      <c r="F14" s="125"/>
-      <c r="G14" s="125"/>
-      <c r="H14" s="126"/>
-    </row>
-    <row r="15" spans="1:8" ht="17" customHeight="1">
+      <c r="C14" s="129"/>
+      <c r="D14" s="129"/>
+      <c r="E14" s="129"/>
+      <c r="F14" s="129"/>
+      <c r="G14" s="129"/>
+      <c r="H14" s="130"/>
+    </row>
+    <row r="15" spans="1:8" ht="17.100000000000001" customHeight="1">
       <c r="A15" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="127" t="s">
+      <c r="B15" s="131" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="128"/>
-      <c r="D15" s="128"/>
-      <c r="E15" s="128"/>
-      <c r="F15" s="128"/>
-      <c r="G15" s="128"/>
-      <c r="H15" s="129"/>
-    </row>
-    <row r="16" spans="1:8" ht="17" customHeight="1">
+      <c r="C15" s="132"/>
+      <c r="D15" s="132"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="132"/>
+      <c r="H15" s="133"/>
+    </row>
+    <row r="16" spans="1:8" ht="17.100000000000001" customHeight="1">
       <c r="A16" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="124" t="s">
+      <c r="B16" s="128" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="125"/>
-      <c r="D16" s="125"/>
-      <c r="E16" s="125"/>
-      <c r="F16" s="125"/>
-      <c r="G16" s="125"/>
-      <c r="H16" s="126"/>
-    </row>
-    <row r="17" spans="1:8" ht="17" customHeight="1">
+      <c r="C16" s="129"/>
+      <c r="D16" s="129"/>
+      <c r="E16" s="129"/>
+      <c r="F16" s="129"/>
+      <c r="G16" s="129"/>
+      <c r="H16" s="130"/>
+    </row>
+    <row r="17" spans="1:8" ht="17.100000000000001" customHeight="1">
       <c r="A17" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="B17" s="127" t="s">
+      <c r="B17" s="131" t="s">
         <v>64</v>
       </c>
-      <c r="C17" s="128"/>
-      <c r="D17" s="128"/>
-      <c r="E17" s="128"/>
-      <c r="F17" s="128"/>
-      <c r="G17" s="128"/>
-      <c r="H17" s="129"/>
-    </row>
-    <row r="18" spans="1:8" ht="17" customHeight="1">
+      <c r="C17" s="132"/>
+      <c r="D17" s="132"/>
+      <c r="E17" s="132"/>
+      <c r="F17" s="132"/>
+      <c r="G17" s="132"/>
+      <c r="H17" s="133"/>
+    </row>
+    <row r="18" spans="1:8" ht="17.100000000000001" customHeight="1">
       <c r="A18" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="124" t="s">
+      <c r="B18" s="128" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="125"/>
-      <c r="D18" s="125"/>
-      <c r="E18" s="125"/>
-      <c r="F18" s="125"/>
-      <c r="G18" s="125"/>
-      <c r="H18" s="126"/>
-    </row>
-    <row r="19" spans="1:8" ht="17" customHeight="1">
+      <c r="C18" s="129"/>
+      <c r="D18" s="129"/>
+      <c r="E18" s="129"/>
+      <c r="F18" s="129"/>
+      <c r="G18" s="129"/>
+      <c r="H18" s="130"/>
+    </row>
+    <row r="19" spans="1:8" ht="17.100000000000001" customHeight="1">
       <c r="A19" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="127" t="s">
+      <c r="B19" s="131" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="128"/>
-      <c r="D19" s="128"/>
-      <c r="E19" s="128"/>
-      <c r="F19" s="128"/>
-      <c r="G19" s="128"/>
-      <c r="H19" s="129"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.5">
-      <c r="A21" s="117" t="s">
+      <c r="C19" s="132"/>
+      <c r="D19" s="132"/>
+      <c r="E19" s="132"/>
+      <c r="F19" s="132"/>
+      <c r="G19" s="132"/>
+      <c r="H19" s="133"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75">
+      <c r="A21" s="118" t="s">
         <v>69</v>
       </c>
-      <c r="B21" s="117"/>
-      <c r="C21" s="117"/>
-      <c r="D21" s="117"/>
-      <c r="E21" s="117"/>
-      <c r="F21" s="117"/>
-      <c r="G21" s="117"/>
-      <c r="H21" s="117"/>
-    </row>
-    <row r="22" spans="1:8" ht="28">
+      <c r="B21" s="118"/>
+      <c r="C21" s="118"/>
+      <c r="D21" s="118"/>
+      <c r="E21" s="118"/>
+      <c r="F21" s="118"/>
+      <c r="G21" s="118"/>
+      <c r="H21" s="118"/>
+    </row>
+    <row r="22" spans="1:8" ht="30">
       <c r="A22" s="1" t="s">
         <v>70</v>
       </c>
@@ -3583,14 +3595,14 @@
       <c r="D22" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E22" s="122" t="s">
+      <c r="E22" s="134" t="s">
         <v>71</v>
       </c>
-      <c r="F22" s="122"/>
-      <c r="G22" s="122"/>
-      <c r="H22" s="123"/>
-    </row>
-    <row r="23" spans="1:8" ht="23" customHeight="1">
+      <c r="F22" s="134"/>
+      <c r="G22" s="134"/>
+      <c r="H22" s="113"/>
+    </row>
+    <row r="23" spans="1:8" ht="23.1" customHeight="1">
       <c r="A23" s="10" t="s">
         <v>72</v>
       </c>
@@ -3603,14 +3615,14 @@
       <c r="D23" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E23" s="120" t="s">
+      <c r="E23" s="135" t="s">
         <v>73</v>
       </c>
-      <c r="F23" s="120"/>
-      <c r="G23" s="120"/>
-      <c r="H23" s="121"/>
-    </row>
-    <row r="24" spans="1:8" ht="23" customHeight="1">
+      <c r="F23" s="135"/>
+      <c r="G23" s="135"/>
+      <c r="H23" s="136"/>
+    </row>
+    <row r="24" spans="1:8" ht="23.1" customHeight="1">
       <c r="A24" s="4" t="s">
         <v>74</v>
       </c>
@@ -3623,14 +3635,14 @@
       <c r="D24" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="118" t="s">
+      <c r="E24" s="137" t="s">
         <v>75</v>
       </c>
-      <c r="F24" s="118"/>
-      <c r="G24" s="118"/>
-      <c r="H24" s="119"/>
-    </row>
-    <row r="25" spans="1:8" ht="23" customHeight="1">
+      <c r="F24" s="137"/>
+      <c r="G24" s="137"/>
+      <c r="H24" s="138"/>
+    </row>
+    <row r="25" spans="1:8" ht="23.1" customHeight="1">
       <c r="A25" s="10" t="s">
         <v>76</v>
       </c>
@@ -3643,12 +3655,12 @@
       <c r="D25" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E25" s="120" t="s">
+      <c r="E25" s="135" t="s">
         <v>77</v>
       </c>
-      <c r="F25" s="120"/>
-      <c r="G25" s="120"/>
-      <c r="H25" s="121"/>
+      <c r="F25" s="135"/>
+      <c r="G25" s="135"/>
+      <c r="H25" s="136"/>
     </row>
     <row r="26" spans="1:8" ht="40.5" customHeight="1">
       <c r="A26" s="4" t="s">
@@ -3663,26 +3675,26 @@
       <c r="D26" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E26" s="118" t="s">
+      <c r="E26" s="137" t="s">
         <v>79</v>
       </c>
-      <c r="F26" s="118"/>
-      <c r="G26" s="118"/>
-      <c r="H26" s="119"/>
-    </row>
-    <row r="28" spans="1:8" ht="15.5">
-      <c r="A28" s="117" t="s">
+      <c r="F26" s="137"/>
+      <c r="G26" s="137"/>
+      <c r="H26" s="138"/>
+    </row>
+    <row r="28" spans="1:8" ht="15.75">
+      <c r="A28" s="118" t="s">
         <v>80</v>
       </c>
-      <c r="B28" s="117"/>
-      <c r="C28" s="117"/>
-      <c r="D28" s="117"/>
-      <c r="E28" s="117"/>
-      <c r="F28" s="117"/>
-      <c r="G28" s="117"/>
-      <c r="H28" s="117"/>
-    </row>
-    <row r="29" spans="1:8" ht="28">
+      <c r="B28" s="118"/>
+      <c r="C28" s="118"/>
+      <c r="D28" s="118"/>
+      <c r="E28" s="118"/>
+      <c r="F28" s="118"/>
+      <c r="G28" s="118"/>
+      <c r="H28" s="118"/>
+    </row>
+    <row r="29" spans="1:8" ht="30">
       <c r="A29" s="1" t="s">
         <v>81</v>
       </c>
@@ -3698,11 +3710,11 @@
       <c r="E29" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F29" s="122"/>
-      <c r="G29" s="122"/>
-      <c r="H29" s="123"/>
-    </row>
-    <row r="30" spans="1:8" ht="53.5" customHeight="1">
+      <c r="F29" s="134"/>
+      <c r="G29" s="134"/>
+      <c r="H29" s="113"/>
+    </row>
+    <row r="30" spans="1:8" ht="53.45" customHeight="1">
       <c r="A30" s="40" t="s">
         <v>84</v>
       </c>
@@ -3718,11 +3730,11 @@
       <c r="E30" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F30" s="120"/>
-      <c r="G30" s="120"/>
-      <c r="H30" s="121"/>
-    </row>
-    <row r="31" spans="1:8" ht="32" customHeight="1">
+      <c r="F30" s="135"/>
+      <c r="G30" s="135"/>
+      <c r="H30" s="136"/>
+    </row>
+    <row r="31" spans="1:8" ht="32.1" customHeight="1">
       <c r="A31" s="41" t="s">
         <v>86</v>
       </c>
@@ -3738,11 +3750,11 @@
       <c r="E31" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F31" s="118"/>
-      <c r="G31" s="118"/>
-      <c r="H31" s="119"/>
-    </row>
-    <row r="32" spans="1:8" ht="32" customHeight="1">
+      <c r="F31" s="137"/>
+      <c r="G31" s="137"/>
+      <c r="H31" s="138"/>
+    </row>
+    <row r="32" spans="1:8" ht="32.1" customHeight="1">
       <c r="A32" s="40" t="s">
         <v>88</v>
       </c>
@@ -3758,11 +3770,11 @@
       <c r="E32" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F32" s="120"/>
-      <c r="G32" s="120"/>
-      <c r="H32" s="121"/>
-    </row>
-    <row r="33" spans="1:8" ht="32" customHeight="1">
+      <c r="F32" s="135"/>
+      <c r="G32" s="135"/>
+      <c r="H32" s="136"/>
+    </row>
+    <row r="33" spans="1:8" ht="32.1" customHeight="1">
       <c r="A33" s="41" t="s">
         <v>90</v>
       </c>
@@ -3778,11 +3790,11 @@
       <c r="E33" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F33" s="118"/>
-      <c r="G33" s="118"/>
-      <c r="H33" s="119"/>
-    </row>
-    <row r="34" spans="1:8" ht="32" customHeight="1">
+      <c r="F33" s="137"/>
+      <c r="G33" s="137"/>
+      <c r="H33" s="138"/>
+    </row>
+    <row r="34" spans="1:8" ht="32.1" customHeight="1">
       <c r="A34" s="40" t="s">
         <v>92</v>
       </c>
@@ -3798,11 +3810,11 @@
       <c r="E34" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F34" s="120"/>
-      <c r="G34" s="120"/>
-      <c r="H34" s="121"/>
-    </row>
-    <row r="35" spans="1:8" ht="32" customHeight="1">
+      <c r="F34" s="135"/>
+      <c r="G34" s="135"/>
+      <c r="H34" s="136"/>
+    </row>
+    <row r="35" spans="1:8" ht="32.1" customHeight="1">
       <c r="A35" s="41" t="s">
         <v>94</v>
       </c>
@@ -3818,11 +3830,11 @@
       <c r="E35" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F35" s="118"/>
-      <c r="G35" s="118"/>
-      <c r="H35" s="119"/>
-    </row>
-    <row r="36" spans="1:8" ht="32" customHeight="1">
+      <c r="F35" s="137"/>
+      <c r="G35" s="137"/>
+      <c r="H35" s="138"/>
+    </row>
+    <row r="36" spans="1:8" ht="32.1" customHeight="1">
       <c r="A36" s="40" t="s">
         <v>96</v>
       </c>
@@ -3838,110 +3850,138 @@
       <c r="E36" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F36" s="120"/>
-      <c r="G36" s="120"/>
-      <c r="H36" s="121"/>
-    </row>
-    <row r="38" spans="1:8" ht="15.5">
-      <c r="A38" s="117" t="s">
+      <c r="F36" s="135"/>
+      <c r="G36" s="135"/>
+      <c r="H36" s="136"/>
+    </row>
+    <row r="38" spans="1:8" ht="15.75">
+      <c r="A38" s="118" t="s">
         <v>98</v>
       </c>
-      <c r="B38" s="117"/>
-      <c r="C38" s="117"/>
-      <c r="D38" s="117"/>
-      <c r="E38" s="117"/>
-      <c r="F38" s="117"/>
-      <c r="G38" s="117"/>
-      <c r="H38" s="117"/>
+      <c r="B38" s="118"/>
+      <c r="C38" s="118"/>
+      <c r="D38" s="118"/>
+      <c r="E38" s="118"/>
+      <c r="F38" s="118"/>
+      <c r="G38" s="118"/>
+      <c r="H38" s="118"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="108" t="s">
+      <c r="A39" s="139" t="s">
         <v>99</v>
       </c>
-      <c r="B39" s="109"/>
-      <c r="C39" s="109"/>
-      <c r="D39" s="109"/>
-      <c r="E39" s="109"/>
-      <c r="F39" s="109"/>
-      <c r="G39" s="109"/>
-      <c r="H39" s="110"/>
+      <c r="B39" s="140"/>
+      <c r="C39" s="140"/>
+      <c r="D39" s="140"/>
+      <c r="E39" s="140"/>
+      <c r="F39" s="140"/>
+      <c r="G39" s="140"/>
+      <c r="H39" s="141"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="111"/>
-      <c r="B40" s="112"/>
-      <c r="C40" s="112"/>
-      <c r="D40" s="112"/>
-      <c r="E40" s="112"/>
-      <c r="F40" s="112"/>
-      <c r="G40" s="112"/>
-      <c r="H40" s="113"/>
+      <c r="A40" s="142"/>
+      <c r="B40" s="143"/>
+      <c r="C40" s="143"/>
+      <c r="D40" s="143"/>
+      <c r="E40" s="143"/>
+      <c r="F40" s="143"/>
+      <c r="G40" s="143"/>
+      <c r="H40" s="144"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="111"/>
-      <c r="B41" s="112"/>
-      <c r="C41" s="112"/>
-      <c r="D41" s="112"/>
-      <c r="E41" s="112"/>
-      <c r="F41" s="112"/>
-      <c r="G41" s="112"/>
-      <c r="H41" s="113"/>
+      <c r="A41" s="142"/>
+      <c r="B41" s="143"/>
+      <c r="C41" s="143"/>
+      <c r="D41" s="143"/>
+      <c r="E41" s="143"/>
+      <c r="F41" s="143"/>
+      <c r="G41" s="143"/>
+      <c r="H41" s="144"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="114"/>
-      <c r="B42" s="115"/>
-      <c r="C42" s="115"/>
-      <c r="D42" s="115"/>
-      <c r="E42" s="115"/>
-      <c r="F42" s="115"/>
-      <c r="G42" s="115"/>
-      <c r="H42" s="116"/>
-    </row>
-    <row r="44" spans="1:8" ht="15.5">
-      <c r="A44" s="117" t="s">
+      <c r="A42" s="145"/>
+      <c r="B42" s="146"/>
+      <c r="C42" s="146"/>
+      <c r="D42" s="146"/>
+      <c r="E42" s="146"/>
+      <c r="F42" s="146"/>
+      <c r="G42" s="146"/>
+      <c r="H42" s="147"/>
+    </row>
+    <row r="44" spans="1:8" ht="15.75">
+      <c r="A44" s="118" t="s">
         <v>100</v>
       </c>
-      <c r="B44" s="117"/>
-      <c r="C44" s="117"/>
-      <c r="D44" s="117"/>
-      <c r="E44" s="117"/>
-      <c r="F44" s="117"/>
-      <c r="G44" s="117"/>
-      <c r="H44" s="117"/>
+      <c r="B44" s="118"/>
+      <c r="C44" s="118"/>
+      <c r="D44" s="118"/>
+      <c r="E44" s="118"/>
+      <c r="F44" s="118"/>
+      <c r="G44" s="118"/>
+      <c r="H44" s="118"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="108" t="s">
+      <c r="A45" s="139" t="s">
         <v>101</v>
       </c>
-      <c r="B45" s="109"/>
-      <c r="C45" s="109"/>
-      <c r="D45" s="109"/>
-      <c r="E45" s="109"/>
-      <c r="F45" s="109"/>
-      <c r="G45" s="109"/>
-      <c r="H45" s="110"/>
+      <c r="B45" s="140"/>
+      <c r="C45" s="140"/>
+      <c r="D45" s="140"/>
+      <c r="E45" s="140"/>
+      <c r="F45" s="140"/>
+      <c r="G45" s="140"/>
+      <c r="H45" s="141"/>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="111"/>
-      <c r="B46" s="112"/>
-      <c r="C46" s="112"/>
-      <c r="D46" s="112"/>
-      <c r="E46" s="112"/>
-      <c r="F46" s="112"/>
-      <c r="G46" s="112"/>
-      <c r="H46" s="113"/>
+      <c r="A46" s="142"/>
+      <c r="B46" s="143"/>
+      <c r="C46" s="143"/>
+      <c r="D46" s="143"/>
+      <c r="E46" s="143"/>
+      <c r="F46" s="143"/>
+      <c r="G46" s="143"/>
+      <c r="H46" s="144"/>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="114"/>
-      <c r="B47" s="115"/>
-      <c r="C47" s="115"/>
-      <c r="D47" s="115"/>
-      <c r="E47" s="115"/>
-      <c r="F47" s="115"/>
-      <c r="G47" s="115"/>
-      <c r="H47" s="116"/>
+      <c r="A47" s="145"/>
+      <c r="B47" s="146"/>
+      <c r="C47" s="146"/>
+      <c r="D47" s="146"/>
+      <c r="E47" s="146"/>
+      <c r="F47" s="146"/>
+      <c r="G47" s="146"/>
+      <c r="H47" s="147"/>
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="A39:H42"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A45:H47"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A9:H11"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="B15:H15"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:B4"/>
@@ -3952,76 +3992,48 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="G5:H6"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A9:H11"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="A39:H42"/>
-    <mergeCell ref="A44:H44"/>
-    <mergeCell ref="A45:H47"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="A38:H38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G31"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" customWidth="1"/>
+    <col min="1" max="1" width="15.375" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="12.5" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" customWidth="1"/>
-    <col min="7" max="7" width="24.9140625" customWidth="1"/>
+    <col min="4" max="4" width="13.375" customWidth="1"/>
+    <col min="5" max="5" width="14.875" customWidth="1"/>
+    <col min="6" max="6" width="15.625" customWidth="1"/>
+    <col min="7" max="7" width="24.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17" customHeight="1">
-      <c r="A1" s="139" t="s">
+    <row r="1" spans="1:7" ht="17.100000000000001" customHeight="1">
+      <c r="A1" s="110" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.5">
-      <c r="A3" s="117" t="s">
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75">
+      <c r="A3" s="118" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="117"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="117"/>
-    </row>
-    <row r="4" spans="1:7" ht="28">
+      <c r="B3" s="118"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
+      <c r="E3" s="118"/>
+      <c r="F3" s="118"/>
+      <c r="G3" s="118"/>
+    </row>
+    <row r="4" spans="1:7" ht="30">
       <c r="A4" s="1" t="s">
         <v>104</v>
       </c>
@@ -4031,14 +4043,14 @@
       <c r="C4" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D4" s="122" t="s">
+      <c r="D4" s="134" t="s">
         <v>107</v>
       </c>
-      <c r="E4" s="122"/>
-      <c r="F4" s="122"/>
-      <c r="G4" s="123"/>
-    </row>
-    <row r="5" spans="1:7" ht="32" customHeight="1">
+      <c r="E4" s="134"/>
+      <c r="F4" s="134"/>
+      <c r="G4" s="113"/>
+    </row>
+    <row r="5" spans="1:7" ht="32.1" customHeight="1">
       <c r="A5" s="10" t="s">
         <v>108</v>
       </c>
@@ -4048,12 +4060,12 @@
       <c r="C5" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="120" t="s">
+      <c r="D5" s="135" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="121"/>
+      <c r="E5" s="135"/>
+      <c r="F5" s="135"/>
+      <c r="G5" s="136"/>
     </row>
     <row r="6" spans="1:7" ht="48" customHeight="1">
       <c r="A6" s="4" t="s">
@@ -4065,14 +4077,14 @@
       <c r="C6" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D6" s="118" t="s">
+      <c r="D6" s="137" t="s">
         <v>114</v>
       </c>
-      <c r="E6" s="118"/>
-      <c r="F6" s="118"/>
-      <c r="G6" s="119"/>
-    </row>
-    <row r="7" spans="1:7" ht="42.5" customHeight="1">
+      <c r="E6" s="137"/>
+      <c r="F6" s="137"/>
+      <c r="G6" s="138"/>
+    </row>
+    <row r="7" spans="1:7" ht="42.6" customHeight="1">
       <c r="A7" s="10" t="s">
         <v>115</v>
       </c>
@@ -4082,16 +4094,16 @@
       <c r="C7" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="D7" s="120" t="s">
+      <c r="D7" s="135" t="s">
         <v>117</v>
       </c>
-      <c r="E7" s="120"/>
-      <c r="F7" s="120"/>
-      <c r="G7" s="121"/>
-    </row>
-    <row r="8" spans="1:7" ht="52" customHeight="1">
+      <c r="E7" s="135"/>
+      <c r="F7" s="135"/>
+      <c r="G7" s="136"/>
+    </row>
+    <row r="8" spans="1:7" ht="51.95" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>316</v>
+        <v>295</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>118</v>
@@ -4099,23 +4111,23 @@
       <c r="C8" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D8" s="118" t="s">
+      <c r="D8" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E8" s="118"/>
-      <c r="F8" s="118"/>
-      <c r="G8" s="119"/>
-    </row>
-    <row r="10" spans="1:7" ht="15.5">
-      <c r="A10" s="117" t="s">
+      <c r="E8" s="137"/>
+      <c r="F8" s="137"/>
+      <c r="G8" s="138"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.75">
+      <c r="A10" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="B10" s="117"/>
-      <c r="C10" s="117"/>
-      <c r="D10" s="117"/>
-      <c r="E10" s="117"/>
-      <c r="F10" s="117"/>
-      <c r="G10" s="117"/>
+      <c r="B10" s="118"/>
+      <c r="C10" s="118"/>
+      <c r="D10" s="118"/>
+      <c r="E10" s="118"/>
+      <c r="F10" s="118"/>
+      <c r="G10" s="118"/>
     </row>
     <row r="11" spans="1:7" ht="25.5" customHeight="1">
       <c r="A11" s="1" t="s">
@@ -4127,48 +4139,48 @@
       <c r="C11" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D11" s="122" t="s">
-        <v>325</v>
-      </c>
-      <c r="E11" s="122"/>
-      <c r="F11" s="122"/>
-      <c r="G11" s="123"/>
-    </row>
-    <row r="12" spans="1:7" ht="46" customHeight="1">
+      <c r="D11" s="134" t="s">
+        <v>304</v>
+      </c>
+      <c r="E11" s="134"/>
+      <c r="F11" s="134"/>
+      <c r="G11" s="113"/>
+    </row>
+    <row r="12" spans="1:7" ht="45.95" customHeight="1">
       <c r="A12" s="66" t="s">
         <v>124</v>
       </c>
       <c r="B12" s="67" t="s">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="C12" s="66" t="s">
-        <v>324</v>
-      </c>
-      <c r="D12" s="146" t="s">
-        <v>323</v>
-      </c>
-      <c r="E12" s="146"/>
-      <c r="F12" s="146"/>
-      <c r="G12" s="147"/>
-    </row>
-    <row r="13" spans="1:7" ht="58" customHeight="1">
+        <v>303</v>
+      </c>
+      <c r="D12" s="148" t="s">
+        <v>302</v>
+      </c>
+      <c r="E12" s="148"/>
+      <c r="F12" s="148"/>
+      <c r="G12" s="149"/>
+    </row>
+    <row r="13" spans="1:7" ht="57.95" customHeight="1">
       <c r="A13" s="66" t="s">
         <v>124</v>
       </c>
       <c r="B13" s="67" t="s">
-        <v>345</v>
+        <v>323</v>
       </c>
       <c r="C13" s="66" t="s">
-        <v>321</v>
-      </c>
-      <c r="D13" s="146" t="s">
-        <v>337</v>
-      </c>
-      <c r="E13" s="146"/>
-      <c r="F13" s="146"/>
-      <c r="G13" s="147"/>
-    </row>
-    <row r="14" spans="1:7" ht="31" customHeight="1">
+        <v>300</v>
+      </c>
+      <c r="D13" s="148" t="s">
+        <v>315</v>
+      </c>
+      <c r="E13" s="148"/>
+      <c r="F13" s="148"/>
+      <c r="G13" s="149"/>
+    </row>
+    <row r="14" spans="1:7" ht="30.95" customHeight="1">
       <c r="A14" s="66" t="s">
         <v>124</v>
       </c>
@@ -4176,50 +4188,50 @@
         <v>112</v>
       </c>
       <c r="C14" s="66" t="s">
-        <v>324</v>
-      </c>
-      <c r="D14" s="146" t="s">
-        <v>323</v>
-      </c>
-      <c r="E14" s="146"/>
-      <c r="F14" s="146"/>
-      <c r="G14" s="147"/>
-    </row>
-    <row r="15" spans="1:7" ht="43" customHeight="1">
+        <v>303</v>
+      </c>
+      <c r="D14" s="148" t="s">
+        <v>302</v>
+      </c>
+      <c r="E14" s="148"/>
+      <c r="F14" s="148"/>
+      <c r="G14" s="149"/>
+    </row>
+    <row r="15" spans="1:7" ht="42.95" customHeight="1">
       <c r="A15" s="66" t="s">
         <v>124</v>
       </c>
       <c r="B15" s="67" t="s">
-        <v>320</v>
+        <v>299</v>
       </c>
       <c r="C15" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="146" t="s">
-        <v>339</v>
-      </c>
-      <c r="E15" s="146"/>
-      <c r="F15" s="146"/>
-      <c r="G15" s="147"/>
+      <c r="D15" s="148" t="s">
+        <v>317</v>
+      </c>
+      <c r="E15" s="148"/>
+      <c r="F15" s="148"/>
+      <c r="G15" s="149"/>
     </row>
     <row r="16" spans="1:7" ht="33" customHeight="1">
       <c r="A16" s="66" t="s">
         <v>124</v>
       </c>
       <c r="B16" s="68" t="s">
-        <v>316</v>
+        <v>295</v>
       </c>
       <c r="C16" s="66" t="s">
-        <v>322</v>
-      </c>
-      <c r="D16" s="146" t="s">
-        <v>333</v>
-      </c>
-      <c r="E16" s="146"/>
-      <c r="F16" s="146"/>
-      <c r="G16" s="147"/>
-    </row>
-    <row r="17" spans="1:7" ht="33.5" customHeight="1">
+        <v>301</v>
+      </c>
+      <c r="D16" s="148" t="s">
+        <v>311</v>
+      </c>
+      <c r="E16" s="148"/>
+      <c r="F16" s="148"/>
+      <c r="G16" s="149"/>
+    </row>
+    <row r="17" spans="1:7" ht="33.6" customHeight="1">
       <c r="A17" s="69" t="s">
         <v>125</v>
       </c>
@@ -4229,14 +4241,14 @@
       <c r="C17" s="66" t="s">
         <v>127</v>
       </c>
-      <c r="D17" s="146" t="s">
-        <v>334</v>
-      </c>
-      <c r="E17" s="146"/>
-      <c r="F17" s="146"/>
-      <c r="G17" s="147"/>
-    </row>
-    <row r="18" spans="1:7" ht="32" customHeight="1">
+      <c r="D17" s="148" t="s">
+        <v>312</v>
+      </c>
+      <c r="E17" s="148"/>
+      <c r="F17" s="148"/>
+      <c r="G17" s="149"/>
+    </row>
+    <row r="18" spans="1:7" ht="32.1" customHeight="1">
       <c r="A18" s="69" t="s">
         <v>128</v>
       </c>
@@ -4246,14 +4258,14 @@
       <c r="C18" s="66" t="s">
         <v>130</v>
       </c>
-      <c r="D18" s="146" t="s">
-        <v>335</v>
-      </c>
-      <c r="E18" s="146"/>
-      <c r="F18" s="146"/>
-      <c r="G18" s="147"/>
-    </row>
-    <row r="19" spans="1:7" ht="30.5" customHeight="1">
+      <c r="D18" s="148" t="s">
+        <v>313</v>
+      </c>
+      <c r="E18" s="148"/>
+      <c r="F18" s="148"/>
+      <c r="G18" s="149"/>
+    </row>
+    <row r="19" spans="1:7" ht="30.6" customHeight="1">
       <c r="A19" s="69" t="s">
         <v>128</v>
       </c>
@@ -4263,14 +4275,14 @@
       <c r="C19" s="66" t="s">
         <v>132</v>
       </c>
-      <c r="D19" s="146" t="s">
-        <v>338</v>
-      </c>
-      <c r="E19" s="146"/>
-      <c r="F19" s="146"/>
-      <c r="G19" s="147"/>
-    </row>
-    <row r="20" spans="1:7" ht="44" customHeight="1">
+      <c r="D19" s="148" t="s">
+        <v>316</v>
+      </c>
+      <c r="E19" s="148"/>
+      <c r="F19" s="148"/>
+      <c r="G19" s="149"/>
+    </row>
+    <row r="20" spans="1:7" ht="44.1" customHeight="1">
       <c r="A20" s="69" t="s">
         <v>128</v>
       </c>
@@ -4280,25 +4292,25 @@
       <c r="C20" s="66" t="s">
         <v>134</v>
       </c>
-      <c r="D20" s="146" t="s">
-        <v>336</v>
-      </c>
-      <c r="E20" s="146"/>
-      <c r="F20" s="146"/>
-      <c r="G20" s="147"/>
-    </row>
-    <row r="23" spans="1:7" ht="15.5">
-      <c r="A23" s="117" t="s">
+      <c r="D20" s="148" t="s">
+        <v>314</v>
+      </c>
+      <c r="E20" s="148"/>
+      <c r="F20" s="148"/>
+      <c r="G20" s="149"/>
+    </row>
+    <row r="23" spans="1:7" ht="15.75">
+      <c r="A23" s="118" t="s">
         <v>135</v>
       </c>
-      <c r="B23" s="117"/>
-      <c r="C23" s="117"/>
-      <c r="D23" s="117"/>
-      <c r="E23" s="117"/>
-      <c r="F23" s="117"/>
-      <c r="G23" s="117"/>
-    </row>
-    <row r="24" spans="1:7" ht="42">
+      <c r="B23" s="118"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="118"/>
+      <c r="G23" s="118"/>
+    </row>
+    <row r="24" spans="1:7" ht="45">
       <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
@@ -4311,11 +4323,11 @@
       <c r="D24" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E24" s="122" t="s">
+      <c r="E24" s="134" t="s">
         <v>138</v>
       </c>
-      <c r="F24" s="122"/>
-      <c r="G24" s="123"/>
+      <c r="F24" s="134"/>
+      <c r="G24" s="113"/>
     </row>
     <row r="25" spans="1:7" ht="24" customHeight="1">
       <c r="A25" s="40" t="s">
@@ -4330,11 +4342,11 @@
       <c r="D25" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E25" s="120" t="s">
+      <c r="E25" s="135" t="s">
         <v>142</v>
       </c>
-      <c r="F25" s="120"/>
-      <c r="G25" s="121"/>
+      <c r="F25" s="135"/>
+      <c r="G25" s="136"/>
     </row>
     <row r="26" spans="1:7" ht="24" customHeight="1">
       <c r="A26" s="41" t="s">
@@ -4349,11 +4361,11 @@
       <c r="D26" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E26" s="118" t="s">
+      <c r="E26" s="137" t="s">
         <v>146</v>
       </c>
-      <c r="F26" s="118"/>
-      <c r="G26" s="119"/>
+      <c r="F26" s="137"/>
+      <c r="G26" s="138"/>
     </row>
     <row r="27" spans="1:7" ht="24" customHeight="1">
       <c r="A27" s="40" t="s">
@@ -4368,11 +4380,11 @@
       <c r="D27" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E27" s="120" t="s">
+      <c r="E27" s="135" t="s">
         <v>149</v>
       </c>
-      <c r="F27" s="120"/>
-      <c r="G27" s="121"/>
+      <c r="F27" s="135"/>
+      <c r="G27" s="136"/>
     </row>
     <row r="28" spans="1:7" ht="24" customHeight="1">
       <c r="A28" s="41" t="s">
@@ -4387,11 +4399,11 @@
       <c r="D28" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E28" s="118" t="s">
+      <c r="E28" s="137" t="s">
         <v>151</v>
       </c>
-      <c r="F28" s="118"/>
-      <c r="G28" s="119"/>
+      <c r="F28" s="137"/>
+      <c r="G28" s="138"/>
     </row>
     <row r="29" spans="1:7" ht="24" customHeight="1">
       <c r="A29" s="40" t="s">
@@ -4406,11 +4418,11 @@
       <c r="D29" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="120" t="s">
+      <c r="E29" s="135" t="s">
         <v>155</v>
       </c>
-      <c r="F29" s="120"/>
-      <c r="G29" s="121"/>
+      <c r="F29" s="135"/>
+      <c r="G29" s="136"/>
     </row>
     <row r="30" spans="1:7" ht="24" customHeight="1">
       <c r="A30" s="41" t="s">
@@ -4425,11 +4437,11 @@
       <c r="D30" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E30" s="118" t="s">
+      <c r="E30" s="137" t="s">
         <v>158</v>
       </c>
-      <c r="F30" s="118"/>
-      <c r="G30" s="119"/>
+      <c r="F30" s="137"/>
+      <c r="G30" s="138"/>
     </row>
     <row r="31" spans="1:7" ht="24" customHeight="1">
       <c r="A31" s="40" t="s">
@@ -4444,19 +4456,24 @@
       <c r="D31" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E31" s="120" t="s">
+      <c r="E31" s="135" t="s">
         <v>161</v>
       </c>
-      <c r="F31" s="120"/>
-      <c r="G31" s="121"/>
+      <c r="F31" s="135"/>
+      <c r="G31" s="136"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="D4:G4"/>
-    <mergeCell ref="D5:G5"/>
-    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="E26:G26"/>
     <mergeCell ref="D13:G13"/>
     <mergeCell ref="D17:G17"/>
     <mergeCell ref="D18:G18"/>
@@ -4469,25 +4486,20 @@
     <mergeCell ref="D14:G14"/>
     <mergeCell ref="D15:G15"/>
     <mergeCell ref="D16:G16"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="E28:G28"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="D6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H29"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -4496,31 +4508,31 @@
     <col min="6" max="8" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17" customHeight="1">
-      <c r="A1" s="139" t="s">
+    <row r="1" spans="1:8" ht="17.100000000000001" customHeight="1">
+      <c r="A1" s="110" t="s">
         <v>162</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-    </row>
-    <row r="3" spans="1:8" ht="22" customHeight="1">
-      <c r="A3" s="157" t="s">
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.95" customHeight="1">
+      <c r="A3" s="150" t="s">
         <v>163</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="158"/>
-      <c r="D3" s="158"/>
-      <c r="E3" s="158"/>
-      <c r="F3" s="158"/>
-      <c r="G3" s="158"/>
-      <c r="H3" s="159"/>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="B3" s="151"/>
+      <c r="C3" s="151"/>
+      <c r="D3" s="151"/>
+      <c r="E3" s="151"/>
+      <c r="F3" s="151"/>
+      <c r="G3" s="151"/>
+      <c r="H3" s="152"/>
+    </row>
+    <row r="5" spans="1:8" ht="30">
       <c r="A5" s="1" t="s">
         <v>164</v>
       </c>
@@ -4536,11 +4548,11 @@
       <c r="E5" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="F5" s="122" t="s">
+      <c r="F5" s="134" t="s">
         <v>169</v>
       </c>
-      <c r="G5" s="122"/>
-      <c r="H5" s="123"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="113"/>
     </row>
     <row r="6" spans="1:8" ht="33" customHeight="1">
       <c r="A6" s="10" t="s">
@@ -4558,11 +4570,11 @@
       <c r="E6" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="F6" s="120" t="s">
+      <c r="F6" s="135" t="s">
         <v>174</v>
       </c>
-      <c r="G6" s="120"/>
-      <c r="H6" s="121"/>
+      <c r="G6" s="135"/>
+      <c r="H6" s="136"/>
     </row>
     <row r="7" spans="1:8" ht="33" customHeight="1">
       <c r="A7" s="4" t="s">
@@ -4580,11 +4592,11 @@
       <c r="E7" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="F7" s="118" t="s">
+      <c r="F7" s="137" t="s">
         <v>178</v>
       </c>
-      <c r="G7" s="118"/>
-      <c r="H7" s="119"/>
+      <c r="G7" s="137"/>
+      <c r="H7" s="138"/>
     </row>
     <row r="8" spans="1:8" ht="33" customHeight="1">
       <c r="A8" s="10" t="s">
@@ -4602,11 +4614,11 @@
       <c r="E8" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="F8" s="120" t="s">
+      <c r="F8" s="135" t="s">
         <v>183</v>
       </c>
-      <c r="G8" s="120"/>
-      <c r="H8" s="121"/>
+      <c r="G8" s="135"/>
+      <c r="H8" s="136"/>
     </row>
     <row r="9" spans="1:8" ht="33" customHeight="1">
       <c r="A9" s="4" t="s">
@@ -4624,11 +4636,11 @@
       <c r="E9" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="F9" s="118" t="s">
+      <c r="F9" s="137" t="s">
         <v>187</v>
       </c>
-      <c r="G9" s="118"/>
-      <c r="H9" s="119"/>
+      <c r="G9" s="137"/>
+      <c r="H9" s="138"/>
     </row>
     <row r="10" spans="1:8" ht="33" customHeight="1">
       <c r="A10" s="10" t="s">
@@ -4646,13 +4658,13 @@
       <c r="E10" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="F10" s="120" t="s">
+      <c r="F10" s="135" t="s">
         <v>192</v>
       </c>
-      <c r="G10" s="120"/>
-      <c r="H10" s="121"/>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="G10" s="135"/>
+      <c r="H10" s="136"/>
+    </row>
+    <row r="11" spans="1:8" ht="15">
       <c r="A11" s="42" t="s">
         <v>193</v>
       </c>
@@ -4667,63 +4679,63 @@
       <c r="G11" s="43"/>
       <c r="H11" s="44"/>
     </row>
-    <row r="13" spans="1:8" ht="15.5">
-      <c r="A13" s="117" t="s">
+    <row r="13" spans="1:8" ht="15.75">
+      <c r="A13" s="118" t="s">
         <v>194</v>
       </c>
-      <c r="B13" s="117"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="117"/>
-      <c r="E13" s="117"/>
-      <c r="F13" s="117"/>
-      <c r="G13" s="117"/>
-      <c r="H13" s="117"/>
+      <c r="B13" s="118"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="118"/>
+      <c r="F13" s="118"/>
+      <c r="G13" s="118"/>
+      <c r="H13" s="118"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="108" t="s">
+      <c r="A14" s="139" t="s">
         <v>195</v>
       </c>
-      <c r="B14" s="109"/>
-      <c r="C14" s="109"/>
-      <c r="D14" s="109"/>
-      <c r="E14" s="109"/>
-      <c r="F14" s="109"/>
-      <c r="G14" s="109"/>
-      <c r="H14" s="110"/>
+      <c r="B14" s="140"/>
+      <c r="C14" s="140"/>
+      <c r="D14" s="140"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="140"/>
+      <c r="G14" s="140"/>
+      <c r="H14" s="141"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="111"/>
-      <c r="B15" s="112"/>
-      <c r="C15" s="112"/>
-      <c r="D15" s="112"/>
-      <c r="E15" s="112"/>
-      <c r="F15" s="112"/>
-      <c r="G15" s="112"/>
-      <c r="H15" s="113"/>
+      <c r="A15" s="142"/>
+      <c r="B15" s="143"/>
+      <c r="C15" s="143"/>
+      <c r="D15" s="143"/>
+      <c r="E15" s="143"/>
+      <c r="F15" s="143"/>
+      <c r="G15" s="143"/>
+      <c r="H15" s="144"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="114"/>
-      <c r="B16" s="115"/>
-      <c r="C16" s="115"/>
-      <c r="D16" s="115"/>
-      <c r="E16" s="115"/>
-      <c r="F16" s="115"/>
-      <c r="G16" s="115"/>
-      <c r="H16" s="116"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.5">
-      <c r="A18" s="117" t="s">
+      <c r="A16" s="145"/>
+      <c r="B16" s="146"/>
+      <c r="C16" s="146"/>
+      <c r="D16" s="146"/>
+      <c r="E16" s="146"/>
+      <c r="F16" s="146"/>
+      <c r="G16" s="146"/>
+      <c r="H16" s="147"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75">
+      <c r="A18" s="118" t="s">
         <v>196</v>
       </c>
-      <c r="B18" s="117"/>
-      <c r="C18" s="117"/>
-      <c r="D18" s="117"/>
-      <c r="E18" s="117"/>
-      <c r="F18" s="117"/>
-      <c r="G18" s="117"/>
-      <c r="H18" s="117"/>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="B18" s="118"/>
+      <c r="C18" s="118"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="118"/>
+      <c r="G18" s="118"/>
+      <c r="H18" s="118"/>
+    </row>
+    <row r="19" spans="1:8" ht="15">
       <c r="A19" s="1" t="s">
         <v>197</v>
       </c>
@@ -4793,67 +4805,62 @@
         <v>216</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.5">
-      <c r="A25" s="117" t="s">
+    <row r="25" spans="1:8" ht="15.75">
+      <c r="A25" s="118" t="s">
         <v>217</v>
       </c>
-      <c r="B25" s="117"/>
-      <c r="C25" s="117"/>
-      <c r="D25" s="117"/>
-      <c r="E25" s="117"/>
-      <c r="F25" s="117"/>
-      <c r="G25" s="117"/>
-      <c r="H25" s="117"/>
+      <c r="B25" s="118"/>
+      <c r="C25" s="118"/>
+      <c r="D25" s="118"/>
+      <c r="E25" s="118"/>
+      <c r="F25" s="118"/>
+      <c r="G25" s="118"/>
+      <c r="H25" s="118"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="148" t="s">
+      <c r="A26" s="153" t="s">
         <v>218</v>
       </c>
-      <c r="B26" s="149"/>
-      <c r="C26" s="149"/>
-      <c r="D26" s="149"/>
-      <c r="E26" s="149"/>
-      <c r="F26" s="149"/>
-      <c r="G26" s="149"/>
-      <c r="H26" s="150"/>
+      <c r="B26" s="154"/>
+      <c r="C26" s="154"/>
+      <c r="D26" s="154"/>
+      <c r="E26" s="154"/>
+      <c r="F26" s="154"/>
+      <c r="G26" s="154"/>
+      <c r="H26" s="155"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="151"/>
-      <c r="B27" s="152"/>
-      <c r="C27" s="152"/>
-      <c r="D27" s="152"/>
-      <c r="E27" s="152"/>
-      <c r="F27" s="152"/>
-      <c r="G27" s="152"/>
-      <c r="H27" s="153"/>
+      <c r="A27" s="156"/>
+      <c r="B27" s="157"/>
+      <c r="C27" s="157"/>
+      <c r="D27" s="157"/>
+      <c r="E27" s="157"/>
+      <c r="F27" s="157"/>
+      <c r="G27" s="157"/>
+      <c r="H27" s="158"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="151"/>
-      <c r="B28" s="152"/>
-      <c r="C28" s="152"/>
-      <c r="D28" s="152"/>
-      <c r="E28" s="152"/>
-      <c r="F28" s="152"/>
-      <c r="G28" s="152"/>
-      <c r="H28" s="153"/>
+      <c r="A28" s="156"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="157"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="157"/>
+      <c r="F28" s="157"/>
+      <c r="G28" s="157"/>
+      <c r="H28" s="158"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="154"/>
-      <c r="B29" s="155"/>
-      <c r="C29" s="155"/>
-      <c r="D29" s="155"/>
-      <c r="E29" s="155"/>
-      <c r="F29" s="155"/>
-      <c r="G29" s="155"/>
-      <c r="H29" s="156"/>
+      <c r="A29" s="159"/>
+      <c r="B29" s="160"/>
+      <c r="C29" s="160"/>
+      <c r="D29" s="160"/>
+      <c r="E29" s="160"/>
+      <c r="F29" s="160"/>
+      <c r="G29" s="160"/>
+      <c r="H29" s="161"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="F7:H7"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A25:H25"/>
     <mergeCell ref="A26:H29"/>
@@ -4862,15 +4869,20 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A14:H16"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="F7:H7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -4881,31 +4893,31 @@
     <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17" customHeight="1">
-      <c r="A1" s="139" t="s">
+    <row r="1" spans="1:8" ht="17.100000000000001" customHeight="1">
+      <c r="A1" s="110" t="s">
         <v>219</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1">
-      <c r="A2" s="157" t="s">
+      <c r="A2" s="150" t="s">
         <v>220</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="159"/>
-    </row>
-    <row r="4" spans="1:8" ht="22" customHeight="1">
+      <c r="B2" s="151"/>
+      <c r="C2" s="151"/>
+      <c r="D2" s="151"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="151"/>
+      <c r="G2" s="151"/>
+      <c r="H2" s="152"/>
+    </row>
+    <row r="4" spans="1:8" ht="21.95" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>221</v>
       </c>
@@ -5113,19 +5125,19 @@
         <v>261</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.5">
-      <c r="A14" s="117" t="s">
+    <row r="14" spans="1:8" ht="15.75">
+      <c r="A14" s="118" t="s">
         <v>262</v>
       </c>
-      <c r="B14" s="117"/>
-      <c r="C14" s="117"/>
-      <c r="D14" s="117"/>
-      <c r="E14" s="117"/>
-      <c r="F14" s="117"/>
-      <c r="G14" s="117"/>
-      <c r="H14" s="117"/>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="B14" s="118"/>
+      <c r="C14" s="118"/>
+      <c r="D14" s="118"/>
+      <c r="E14" s="118"/>
+      <c r="F14" s="118"/>
+      <c r="G14" s="118"/>
+      <c r="H14" s="118"/>
+    </row>
+    <row r="15" spans="1:8" ht="15">
       <c r="A15" s="1" t="s">
         <v>221</v>
       </c>
